--- a/artfynd/A 59688-2024 artfynd.xlsx
+++ b/artfynd/A 59688-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121714267</v>
+        <v>121712536</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>97067</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åsen, Åsen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>336352</v>
+        <v>336266</v>
       </c>
       <c r="R2" t="n">
-        <v>6609440</v>
+        <v>6609556</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121712536</v>
+        <v>121711873</v>
       </c>
       <c r="B3" t="n">
-        <v>97067</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,38 +799,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åsen, Åsen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>336266</v>
+        <v>336389</v>
       </c>
       <c r="R3" t="n">
-        <v>6609556</v>
+        <v>6609433</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121711873</v>
+        <v>121714267</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -938,7 +938,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>336389</v>
+        <v>336352</v>
       </c>
       <c r="R4" t="n">
-        <v>6609433</v>
+        <v>6609440</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 59688-2024 artfynd.xlsx
+++ b/artfynd/A 59688-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121712536</v>
+        <v>121714143</v>
       </c>
       <c r="B2" t="n">
-        <v>97067</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åsen, Åsen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>336266</v>
+        <v>336330</v>
       </c>
       <c r="R2" t="n">
-        <v>6609556</v>
+        <v>6609450</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>10 bladrosetter 1 blomstängel</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121711873</v>
+        <v>121712536</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>97067</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +808,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åsen, Åsen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>336389</v>
+        <v>336266</v>
       </c>
       <c r="R3" t="n">
-        <v>6609433</v>
+        <v>6609556</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1019,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121714143</v>
+        <v>121711873</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1054,7 +1059,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1063,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>336330</v>
+        <v>336389</v>
       </c>
       <c r="R5" t="n">
-        <v>6609450</v>
+        <v>6609433</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1098,7 +1103,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,12 +1113,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>10 bladrosetter 1 blomstängel</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
